--- a/data/trans_orig/P1438_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1438_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de otro dolor crónico en 2023</t>
+          <t>Población con diagnóstico de otro dolor crónico en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>42705</t>
+          <t>43340</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>65915</t>
+          <t>66488</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>121465</t>
+          <t>121940</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>152925</t>
+          <t>152024</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>171281</t>
+          <t>170647</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>211021</t>
+          <t>210137</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,6%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>447065</t>
+          <t>446492</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>470275</t>
+          <t>469640</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>600243</t>
+          <t>601144</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>631703</t>
+          <t>631228</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>83,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1055128</t>
+          <t>1056012</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1094868</t>
+          <t>1095502</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>83,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,52%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>57265</t>
+          <t>59689</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>105694</t>
+          <t>106205</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>90810</t>
+          <t>93131</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>150489</t>
+          <t>150238</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>166749</t>
+          <t>169208</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>242966</t>
+          <t>241819</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2183914</t>
+          <t>2183403</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2232343</t>
+          <t>2229919</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2085987</t>
+          <t>2086238</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2145666</t>
+          <t>2143345</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4283118</t>
+          <t>4284265</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4359335</t>
+          <t>4356876</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,26%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8935</t>
+          <t>8890</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23991</t>
+          <t>23489</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18340</t>
+          <t>18190</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34346</t>
+          <t>33747</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>31021</t>
+          <t>30339</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>54768</t>
+          <t>52624</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>621914</t>
+          <t>622416</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>636970</t>
+          <t>637015</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>625798</t>
+          <t>626397</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>641804</t>
+          <t>641954</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1251281</t>
+          <t>1253425</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1275028</t>
+          <t>1275710</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,68%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>116878</t>
+          <t>118971</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>178405</t>
+          <t>178099</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>238579</t>
+          <t>238221</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>319517</t>
+          <t>319625</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>384377</t>
+          <t>381254</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>488417</t>
+          <t>480689</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3270089</t>
+          <t>3270395</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3331616</t>
+          <t>3329523</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3330271</t>
+          <t>3330163</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3411209</t>
+          <t>3411567</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6609865</t>
+          <t>6617593</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6713905</t>
+          <t>6717028</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,63%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1438_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1438_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>53547</t>
+          <t>56192</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>43340</t>
+          <t>45016</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>66488</t>
+          <t>70252</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>136293</t>
+          <t>146302</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>121940</t>
+          <t>129605</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>152024</t>
+          <t>163681</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>189841</t>
+          <t>202493</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>170647</t>
+          <t>182360</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>210137</t>
+          <t>224502</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,06%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>459433</t>
+          <t>520352</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>446492</t>
+          <t>506292</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>469640</t>
+          <t>531528</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>616875</t>
+          <t>675013</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>601144</t>
+          <t>657634</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>631228</t>
+          <t>691710</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>80,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>84,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1076308</t>
+          <t>1195366</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1056012</t>
+          <t>1173357</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1095502</t>
+          <t>1215499</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>86,95%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>512980</t>
+          <t>576544</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>512980</t>
+          <t>576544</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>512980</t>
+          <t>576544</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>753168</t>
+          <t>821315</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>753168</t>
+          <t>821315</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>753168</t>
+          <t>821315</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1266149</t>
+          <t>1397859</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1266149</t>
+          <t>1397859</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1266149</t>
+          <t>1397859</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>84054</t>
+          <t>90826</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>59689</t>
+          <t>74919</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>106205</t>
+          <t>109510</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>125479</t>
+          <t>140366</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>93131</t>
+          <t>121754</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>150238</t>
+          <t>160738</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
+          <t>6,47%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
           <t>5,61%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>4,16%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>209533</t>
+          <t>231191</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>169208</t>
+          <t>206763</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>241819</t>
+          <t>256827</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,84%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2205554</t>
+          <t>2138872</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2183403</t>
+          <t>2120188</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2229919</t>
+          <t>2154779</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,34 +1216,34 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2110997</t>
+          <t>2029690</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2086238</t>
+          <t>2009318</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2143345</t>
+          <t>2048302</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
+          <t>93,53%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>92,59%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
           <t>94,39%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>93,28%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>95,84%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>4577</t>
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4316551</t>
+          <t>4168563</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4284265</t>
+          <t>4142927</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4356876</t>
+          <t>4192991</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>95,3%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2289608</t>
+          <t>2229698</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2289608</t>
+          <t>2229698</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2289608</t>
+          <t>2229698</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2236476</t>
+          <t>2170056</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2236476</t>
+          <t>2170056</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2236476</t>
+          <t>2170056</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4526084</t>
+          <t>4399754</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4526084</t>
+          <t>4399754</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4526084</t>
+          <t>4399754</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>15127</t>
+          <t>16711</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8890</t>
+          <t>9939</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23489</t>
+          <t>26098</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>25722</t>
+          <t>29764</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18190</t>
+          <t>21442</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33747</t>
+          <t>39009</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>40848</t>
+          <t>46476</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30339</t>
+          <t>36392</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>52624</t>
+          <t>59427</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>630778</t>
+          <t>694005</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>622416</t>
+          <t>684618</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>637015</t>
+          <t>700777</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>634422</t>
+          <t>703762</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>626397</t>
+          <t>694517</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>641954</t>
+          <t>712084</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1265201</t>
+          <t>1397766</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1253425</t>
+          <t>1384815</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1275710</t>
+          <t>1407850</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,48%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>645905</t>
+          <t>710716</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>645905</t>
+          <t>710716</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>645905</t>
+          <t>710716</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660144</t>
+          <t>733526</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660144</t>
+          <t>733526</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660144</t>
+          <t>733526</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1306049</t>
+          <t>1444242</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1306049</t>
+          <t>1444242</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1306049</t>
+          <t>1444242</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>152728</t>
+          <t>163729</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>118971</t>
+          <t>141708</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>178099</t>
+          <t>188665</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>287494</t>
+          <t>316432</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>238221</t>
+          <t>291257</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>319625</t>
+          <t>344331</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>440222</t>
+          <t>480161</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>381254</t>
+          <t>448317</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>480689</t>
+          <t>515155</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3295766</t>
+          <t>3353229</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3270395</t>
+          <t>3328293</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3329523</t>
+          <t>3375250</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3362294</t>
+          <t>3408465</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3330163</t>
+          <t>3380566</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3411567</t>
+          <t>3433640</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6658060</t>
+          <t>6761694</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6617593</t>
+          <t>6726700</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6717028</t>
+          <t>6793538</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>93,81%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3448494</t>
+          <t>3516958</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3448494</t>
+          <t>3516958</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3448494</t>
+          <t>3516958</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3649788</t>
+          <t>3724897</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3649788</t>
+          <t>3724897</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3649788</t>
+          <t>3724897</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7098282</t>
+          <t>7241855</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7098282</t>
+          <t>7241855</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7098282</t>
+          <t>7241855</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
